--- a/tame_output/ON/bt/strategyON_20240612.xlsx
+++ b/tame_output/ON/bt/strategyON_20240612.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>54.9%</t>
         </is>
       </c>
     </row>
@@ -849,27 +849,27 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-79.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.9%</t>
+          <t>126.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>450.4%</t>
+          <t>453.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-10.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-673.7%</t>
+          <t>-673.5%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1155,22 +1155,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-41.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-22.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-50.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-264.7%</t>
+          <t>-264.6%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-28.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-32.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-22.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.0%</t>
+          <t>-159.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-261.7%</t>
+          <t>-261.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-29.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-152.3%</t>
+          <t>-152.1%</t>
         </is>
       </c>
     </row>
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.959486734119466</v>
+        <v>-9.896875313930094</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8493442228249291</v>
+        <v>-0.8242996547491805</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.170520236326061</v>
+        <v>-2.107908816136688</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.832494753340968</v>
+        <v>1.870061605454592</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.16374490944933</v>
+        <v>-10.10113348925996</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.925534295838232</v>
+        <v>-0.9004897277624835</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.29815918094005</v>
+        <v>-2.235547760750677</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.761424583691217</v>
+        <v>1.798991435804841</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.30555468365612</v>
+        <v>-10.24294326346675</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9777756510365117</v>
+        <v>-0.9527310829607623</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.469437978585626</v>
+        <v>-2.406826558396252</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.663139859588308</v>
+        <v>1.700706711701932</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.23208485198867</v>
+        <v>-10.1694734317993</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9330160168761106</v>
+        <v>-0.9079714488003621</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.395968146918177</v>
+        <v>-2.333356726728804</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.722593460082198</v>
+        <v>1.760160312195822</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.40720926937521</v>
+        <v>-10.34459784918584</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9885105630832109</v>
+        <v>-0.9634659950074624</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.571092564304721</v>
+        <v>-2.508481144115347</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.632074030397789</v>
+        <v>1.669640882511413</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.6416613633897</v>
+        <v>-10.57904994320033</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.089510565590603</v>
+        <v>-1.064465997514854</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.571092564304721</v>
+        <v>-2.508481144115347</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.624854865496193</v>
+        <v>1.662421717609817</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.92946520792694</v>
+        <v>-10.86685378773757</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.211304294179474</v>
+        <v>-1.186259726103726</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.858896408841959</v>
+        <v>-2.796284988652586</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.445500367999874</v>
+        <v>1.483067220113498</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.98225136352727</v>
+        <v>-10.9196399433379</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.231302966581049</v>
+        <v>-1.2062583985053</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.954571895424356</v>
+        <v>-2.891960475234983</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.389210865888992</v>
+        <v>1.426777718002616</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.10828815689556</v>
+        <v>-11.04567673670618</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.27902395529925</v>
+        <v>-1.253979387223501</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.86670885242524</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.407055568203952</v>
+        <v>1.444622420317576</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.05627264292674</v>
+        <v>-10.99366122273737</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.254227414025324</v>
+        <v>-1.229182845949575</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.86670885242524</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.411045903890353</v>
+        <v>1.448612756003977</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.19794448465086</v>
+        <v>-11.13533306446149</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.312371377613713</v>
+        <v>-1.287326809537965</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.86670885242524</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.409570676991611</v>
+        <v>1.447137529105235</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.14835364022603</v>
+        <v>-11.08574222003666</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.277481629678908</v>
+        <v>-1.252437061603159</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.87972942818978</v>
+        <v>-2.817118008000406</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.454378593811384</v>
+        <v>1.491945445925008</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.13554624722125</v>
+        <v>-11.07293482703188</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.285409806123681</v>
+        <v>-1.260365238047932</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.928585203198681</v>
+        <v>-2.865973783009307</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.41201399515936</v>
+        <v>1.449580847272984</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.90970109450184</v>
+        <v>-10.84708967431247</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.185492671999709</v>
+        <v>-1.160448103923959</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.886658527611517</v>
+        <v>-2.824047107422143</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.446749073547867</v>
+        <v>1.484315925661491</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.78512243816425</v>
+        <v>-10.72251101797488</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.134522064908613</v>
+        <v>-1.109477496832863</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.886658527611517</v>
+        <v>-2.824047107422143</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.447888218103926</v>
+        <v>1.48545507021755</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.83801772620854</v>
+        <v>-10.77540630601917</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.153046405964219</v>
+        <v>-1.12800183788847</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.881703181523071</v>
+        <v>-2.819091761333697</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.453495199919101</v>
+        <v>1.491062052032725</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.76588455092066</v>
+        <v>-10.70327313073128</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.118459431610431</v>
+        <v>-1.093414863534681</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.881703181523071</v>
+        <v>-2.819091761333697</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.459228904157738</v>
+        <v>1.496795756271362</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.69451815831101</v>
+        <v>-10.63190673812164</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.099650136960437</v>
+        <v>-1.074605568884688</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.747725368724049</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.492311477329662</v>
+        <v>1.529878329443286</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.43068129110694</v>
+        <v>-10.36806987091757</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.003998871391717</v>
+        <v>-0.9789543033159673</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.747725368724049</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.482427996016754</v>
+        <v>1.519994848130378</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.16343949023854</v>
+        <v>-10.10082807004917</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.898936711543731</v>
+        <v>-0.8738921434679816</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.747725368724049</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.48059343551738</v>
+        <v>1.518160287631004</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.06553245156205</v>
+        <v>-10.00292103137268</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8600742110465958</v>
+        <v>-0.8350296429708464</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.742351039052866</v>
+        <v>-2.679739618863493</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.521084570460253</v>
+        <v>1.558651422573877</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.04157891058609</v>
+        <v>-9.978967490396721</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8498242885107188</v>
+        <v>-0.8247797204349698</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.718397498076909</v>
+        <v>-2.655786077887535</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.536125201191321</v>
+        <v>1.573692053304945</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.777518972263298</v>
+        <v>-9.714907552073925</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7574606293433526</v>
+        <v>-0.7324160612676032</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.391726139564739</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.681300848023247</v>
+        <v>1.718867700136871</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.070439348758461</v>
+        <v>-9.007827928569087</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4774158136017186</v>
+        <v>-0.4523712455259692</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.391726139564739</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.678513814362946</v>
+        <v>1.71608066647657</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.03025505039227</v>
+        <v>-8.967643630202897</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.460998470367401</v>
+        <v>-0.4359539022916517</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.414153261387922</v>
+        <v>-2.351541841198548</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.702968017270502</v>
+        <v>1.740534869384126</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.866855179452909</v>
+        <v>-8.804243759263535</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3962717007708996</v>
+        <v>-0.3712271326951502</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.250753390448559</v>
+        <v>-2.188141970259186</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.800374761054876</v>
+        <v>1.8379416131685</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.633373957223309</v>
+        <v>-8.570762537033936</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2949547830412071</v>
+        <v>-0.2699102149654578</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.017272168218961</v>
+        <v>-1.954660748029587</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.948387923230488</v>
+        <v>1.985954775344112</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.483707566215795</v>
+        <v>-8.421096146026422</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2379804369511609</v>
+        <v>-0.2129358688754115</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.924368676976425</v>
+        <v>-1.861757256787051</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.00123780766305</v>
+        <v>2.038804659776674</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.351432092584908</v>
+        <v>-8.288820672395534</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1897027607517789</v>
+        <v>-0.1646581926760295</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.792093203345538</v>
+        <v>-1.729481783156165</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.075970578588609</v>
+        <v>2.113537430702233</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.160832417911754</v>
+        <v>-8.098220997722381</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1106478301948806</v>
+        <v>-0.08560326211913116</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.601493528672385</v>
+        <v>-1.538882108483012</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.193145444080137</v>
+        <v>2.230712296193762</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.911832619228173</v>
+        <v>-7.8492211990388</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.001858430502210684</v>
+        <v>0.02690299857796008</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.601493528672385</v>
+        <v>-1.538882108483012</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.206051785303796</v>
+        <v>2.24361863741742</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.017422609001278</v>
+        <v>-7.954811188811904</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.16835349500625</v>
+        <v>-0.1433089269305006</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.70708351844549</v>
+        <v>-1.644472098256116</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.014721861840715</v>
+        <v>2.052288713954339</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.036157511119875</v>
+        <v>-7.973546090930501</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1273031139766023</v>
+        <v>-0.1022585459008529</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.712679528105621</v>
+        <v>-1.650068107916247</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.059908597921723</v>
+        <v>2.097475450035347</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.888217469712275</v>
+        <v>-7.825606049522902</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1880060201017302</v>
+        <v>-0.1629614520259808</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.692358612197063</v>
+        <v>-1.62974719200769</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.95222222477869</v>
+        <v>1.989789076892314</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.871059319580981</v>
+        <v>-7.808447899391608</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1898567463026906</v>
+        <v>-0.1648121782269412</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.675200462065769</v>
+        <v>-1.612589041876396</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.953803128603988</v>
+        <v>1.991369980717612</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.827510912810291</v>
+        <v>-7.764899492620917</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1793979956895075</v>
+        <v>-0.1543534276137581</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.675200462065769</v>
+        <v>-1.612589041876396</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.946842516508895</v>
+        <v>1.984409368622519</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.585362519356432</v>
+        <v>-7.522751099167059</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.06807628392682119</v>
+        <v>-0.04303171585107179</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.675200462065769</v>
+        <v>-1.612589041876396</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.961304870890038</v>
+        <v>1.998871723003662</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.477103382233911</v>
+        <v>-7.414491962044537</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.03024050861861749</v>
+        <v>-0.005195940542868094</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.675200462065769</v>
+        <v>-1.612589041876396</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.955836991349233</v>
+        <v>1.993403843462857</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.35381224741678</v>
+        <v>-7.291200827227406</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.01657403931881163</v>
+        <v>0.04161860739456102</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.551909327248639</v>
+        <v>-1.489297907059265</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.027309766250088</v>
+        <v>2.064876618363712</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.332663048513337</v>
+        <v>-7.270051628323963</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.03273469711751398</v>
+        <v>0.05777926519326337</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.530760128345195</v>
+        <v>-1.468148708155822</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.047700263829479</v>
+        <v>2.085267115943103</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.088897606529892</v>
+        <v>-7.026286186340519</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1260215822579425</v>
+        <v>0.1510661503336919</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.530760128345195</v>
+        <v>-1.468148708155822</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.04348097217653</v>
+        <v>2.081047824290154</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.987134786252597</v>
+        <v>-6.924523366063224</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1688510242888763</v>
+        <v>0.1938955923646257</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.517541059952767</v>
+        <v>-1.454929639763393</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.053536727132003</v>
+        <v>2.091103579245627</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.737284392303523</v>
+        <v>-6.674672972114149</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2615332568522084</v>
+        <v>0.2865778249279578</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.517541059952767</v>
+        <v>-1.454929639763393</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.046278802115705</v>
+        <v>2.08384565422933</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.56139229983609</v>
+        <v>-6.498780879646716</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3354892173598305</v>
+        <v>0.3605337854355799</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.517541059952767</v>
+        <v>-1.454929639763393</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.049877925636354</v>
+        <v>2.087444777749978</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.389945836813626</v>
+        <v>-6.327334416624253</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4173953086233695</v>
+        <v>0.4424398766991189</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.346094596930303</v>
+        <v>-1.28348317674093</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.166073309504386</v>
+        <v>2.20364016161801</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.164912837144803</v>
+        <v>-6.10230141695543</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5064289861071956</v>
+        <v>0.531473554182945</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.12106159726148</v>
+        <v>-1.058450177072107</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.300113586921976</v>
+        <v>2.337680439035601</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.101277094910869</v>
+        <v>-6.038665674721496</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5365780840550864</v>
+        <v>0.5616226521308358</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.057425855027546</v>
+        <v>-0.9948144348381723</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.342989833316654</v>
+        <v>2.380556685430278</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.057514913605027</v>
+        <v>-5.994903493415654</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5352772153612189</v>
+        <v>0.5603217834369683</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.057425855027546</v>
+        <v>-0.9948144348381723</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.32418409210045</v>
+        <v>2.361750944214074</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.817084416800167</v>
+        <v>-5.754472996610794</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6331924907080406</v>
+        <v>0.65823705878379</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8169953582226857</v>
+        <v>-0.7543839380333121</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.470185466808243</v>
+        <v>2.507752318921868</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.744841848628973</v>
+        <v>-5.682230428439599</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6660188318113387</v>
+        <v>0.6910633998870881</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8169953582226857</v>
+        <v>-0.7543839380333121</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.474114780643064</v>
+        <v>2.511681632756688</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.691843526347585</v>
+        <v>-5.629232106158211</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6878967446412338</v>
+        <v>0.7129413127169832</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7616590992207468</v>
+        <v>-0.6990476790313732</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.507995119961567</v>
+        <v>2.545561972075191</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.583038640867858</v>
+        <v>-5.520427220678484</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7284167700531179</v>
+        <v>0.7534613381288673</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7616590992207468</v>
+        <v>-0.6990476790313732</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.504993191181561</v>
+        <v>2.542560043295185</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.363017842830847</v>
+        <v>-5.300406422641474</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8180041262785362</v>
+        <v>0.8430486943542856</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6204392541527666</v>
+        <v>-0.557827833963393</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.591304135232963</v>
+        <v>2.628870987346587</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.230150153767569</v>
+        <v>-5.167538733578196</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8870453847056705</v>
+        <v>0.9120899527814199</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6204392541527666</v>
+        <v>-0.557827833963393</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.607198318034786</v>
+        <v>2.64476517014841</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.109977070403071</v>
+        <v>-5.047365650213697</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9362604624917719</v>
+        <v>0.9613050305675213</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5002661707882676</v>
+        <v>-0.437654750598894</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.680448012493788</v>
+        <v>2.718014864607412</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.965304925303333</v>
+        <v>-4.90269350511396</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.004217423093107</v>
+        <v>1.029261991168856</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3555940256885302</v>
+        <v>-0.2929826054991566</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.77733940211507</v>
+        <v>2.814906254228694</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.025179752661026</v>
+        <v>-4.962568332471652</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9663049835514559</v>
+        <v>0.9913495516272053</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4154688530462223</v>
+        <v>-0.3528574328568487</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.72745199710188</v>
+        <v>2.765018849215505</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.938380254882016</v>
+        <v>-4.875768834692643</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.023425275985625</v>
+        <v>1.048469844061375</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4154688530462223</v>
+        <v>-0.3528574328568487</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.749852490424446</v>
+        <v>2.787419342538071</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.940849961343822</v>
+        <v>-4.878238541154449</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.022509794774315</v>
+        <v>1.047554362850065</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4179385595080285</v>
+        <v>-0.3553271393186549</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.748443067920775</v>
+        <v>2.786009920034399</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.009220147667833</v>
+        <v>-4.946608727478459</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.006168642719413</v>
+        <v>1.031213210795163</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4086628604718135</v>
+        <v>-0.3460514402824399</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.765015409817206</v>
+        <v>2.80258226193083</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.117758328583967</v>
+        <v>-5.055146908394593</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9531900789848509</v>
+        <v>0.9782346470606003</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4086628604718135</v>
+        <v>-0.3460514402824399</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.755452118449097</v>
+        <v>2.793018970562721</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.148751487912672</v>
+        <v>-5.086140067723298</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7655023802937557</v>
+        <v>0.7905469483695051</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4086628604718135</v>
+        <v>-0.3460514402824399</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.580161683489484</v>
+        <v>2.617728535603108</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.973277228120203</v>
+        <v>-4.91066580793083</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8402593162025309</v>
+        <v>0.8653038842782803</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4086628604718135</v>
+        <v>-0.3460514402824399</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.584728915481271</v>
+        <v>2.622295767594896</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.084213480761452</v>
+        <v>-5.021602060572079</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7716268439072382</v>
+        <v>0.7966714119829876</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4086628604718135</v>
+        <v>-0.3460514402824399</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.560470944242478</v>
+        <v>2.598037796356103</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.092495554906511</v>
+        <v>-5.029884134717137</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7714453994691204</v>
+        <v>0.7964899675448698</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4169449346168719</v>
+        <v>-0.3543335144274983</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.558633084975349</v>
+        <v>2.596199937088973</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.934569955971218</v>
+        <v>-4.871958535781844</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8447880254753701</v>
+        <v>0.8698325935511195</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.4169449346168719</v>
+        <v>-0.3543335144274983</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.568805471407482</v>
+        <v>2.606372323521106</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.84832649294484</v>
+        <v>-4.785715072755466</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8742316812597815</v>
+        <v>0.8992762493355309</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.4169449346168719</v>
+        <v>-0.3543335144274983</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.563751741981342</v>
+        <v>2.601318594094966</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.89363331234382</v>
+        <v>-4.831021892154446</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8478847289447151</v>
+        <v>0.8729292970204645</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4577550976261027</v>
+        <v>-0.3951436774367291</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.531041419620329</v>
+        <v>2.568608271733953</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.922666417046121</v>
+        <v>-4.860054996856747</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8368233600968962</v>
+        <v>0.8618679281726456</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4577550976261027</v>
+        <v>-0.3951436774367291</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.53159329265343</v>
+        <v>2.569160144767054</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.829855935595261</v>
+        <v>-4.767244515405888</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8032202445686059</v>
+        <v>0.8282648126443553</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3649446161752434</v>
+        <v>-0.3023331959858698</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.516552273415312</v>
+        <v>2.554119125528936</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.874245404924689</v>
+        <v>-4.811633984735315</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7873379327614356</v>
+        <v>0.812382500837185</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.409334085504671</v>
+        <v>-0.3467226653152974</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.491792067742256</v>
+        <v>2.52935891985588</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.761574186688438</v>
+        <v>-4.698962766499065</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8274821285676586</v>
+        <v>0.852526696643408</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2966628672684208</v>
+        <v>-0.2340514470790472</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.554470507195729</v>
+        <v>2.592037359309353</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.649197185505765</v>
+        <v>-4.586585765316392</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.877924224871395</v>
+        <v>0.9029687929471444</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2966628672684208</v>
+        <v>-0.2340514470790472</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.559961803026396</v>
+        <v>2.597528655140021</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.847431754392496</v>
+        <v>-4.784820334203123</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8101275990852419</v>
+        <v>0.8351721671609913</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.4948974361551514</v>
+        <v>-0.4322860159657778</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.452518263462897</v>
+        <v>2.490085115576521</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.930433035417775</v>
+        <v>-4.867821615228402</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6152828066757836</v>
+        <v>0.640327374751533</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.5134683206823252</v>
+        <v>-0.4508569004929516</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.279731452747246</v>
+        <v>2.31729830486087</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.039047113861106</v>
+        <v>-4.976435693671733</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.6919868360176569</v>
+        <v>0.717031404093406</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.5134683206823252</v>
+        <v>-0.4508569004929516</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.399881113466451</v>
+        <v>2.437447965580076</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.125645696842209</v>
+        <v>-5.063034276652836</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6718604289275385</v>
+        <v>0.6969049970032879</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.5134683206823252</v>
+        <v>-0.4508569004929516</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.414394139568774</v>
+        <v>2.451960991682399</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.087262034284058</v>
+        <v>-5.024650614094685</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.6846333352931677</v>
+        <v>0.7096779033689171</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.475084658124174</v>
+        <v>-0.4124732379348004</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.434843778446034</v>
+        <v>2.472410630559658</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.910145704248892</v>
+        <v>-4.847534284059519</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7522088961525359</v>
+        <v>0.7772534642282853</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.475084658124174</v>
+        <v>-0.4124732379348004</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.431572807291336</v>
+        <v>2.46913965940496</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.955237949082438</v>
+        <v>-4.892626528893064</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7348553899810308</v>
+        <v>0.7598999580567802</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.5369807012935638</v>
+        <v>-0.4743692811041902</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.395118573151615</v>
+        <v>2.432685425265239</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.77586252784367</v>
+        <v>-4.713251107654297</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8003925337829523</v>
+        <v>0.8254371018587017</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.3802039431228451</v>
+        <v>-0.3175925229334715</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.482971603360461</v>
+        <v>2.520538455474085</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.820876741364277</v>
+        <v>-4.758265321174903</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7631943037062994</v>
+        <v>0.7882388717820488</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.4105528384374497</v>
+        <v>-0.3479414182480761</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.445569721503288</v>
+        <v>2.483136573616912</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.087881251636712</v>
+        <v>-5.025269831447338</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6620840619362709</v>
+        <v>0.6871286300120203</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.6049158764803984</v>
+        <v>-0.5423044562910246</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.334643461016464</v>
+        <v>2.372210313130088</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.189079033073885</v>
+        <v>-5.126467612884511</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6208088712579034</v>
+        <v>0.6458534393336528</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.6733246900257175</v>
+        <v>-0.6107132698363438</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.292802094785774</v>
+        <v>2.330368946899398</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.156603446903112</v>
+        <v>-5.093992026713739</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6313990672805292</v>
+        <v>0.6564436353562786</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.6733246900257175</v>
+        <v>-0.6107132698363438</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.290402056340091</v>
+        <v>2.327968908453715</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.137565319195815</v>
+        <v>-5.074953899006442</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6355390375716929</v>
+        <v>0.6605836056474423</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.731508301356912</v>
+        <v>-0.6688968811675383</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.252016608749619</v>
+        <v>2.289583460863243</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.168691950346433</v>
+        <v>-5.10608053015706</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.800670254050126</v>
+        <v>0.8257148221258754</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.731508301356912</v>
+        <v>-0.6688968811675383</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.4295984776883</v>
+        <v>2.467165329801924</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.221012330947225</v>
+        <v>-5.158400910757852</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7805754307959427</v>
+        <v>0.8056199988716921</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.6965614413480399</v>
+        <v>-0.6339500211586662</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.451399922679756</v>
+        <v>2.488966774793381</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.241269629476183</v>
+        <v>-5.17865820928681</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7784810417812857</v>
+        <v>0.8035256098570351</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.6965614413480399</v>
+        <v>-0.6339500211586662</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.457408453076682</v>
+        <v>2.494975305190307</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.093526659241181</v>
+        <v>-5.030915239051807</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9167308776673084</v>
+        <v>0.9417754457430578</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.5287540841131567</v>
+        <v>-0.466142663923783</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.637245515209634</v>
+        <v>2.674812367323259</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.195541341772402</v>
+        <v>-5.132929921583028</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8787186261863011</v>
+        <v>0.9037631942620505</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.5287540841131567</v>
+        <v>-0.466142663923783</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.640039136741115</v>
+        <v>2.67760598885474</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.189388635719618</v>
+        <v>-5.126777215530244</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8818420569990733</v>
+        <v>0.9068866250748226</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.5226013780603724</v>
+        <v>-0.4599899578709987</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.644393108764444</v>
+        <v>2.681959960878069</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.206197933870119</v>
+        <v>-5.143586513680746</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8741988144789827</v>
+        <v>0.8992433825547321</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.5394106762108741</v>
+        <v>-0.4767992560215004</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.633388006614254</v>
+        <v>2.670954858727878</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.143899935093997</v>
+        <v>-5.081288514904624</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9654535677862524</v>
+        <v>0.9904981358620017</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.5394106762108741</v>
+        <v>-0.4767992560215004</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.699723560411075</v>
+        <v>2.737290412524699</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.942109737428839</v>
+        <v>-4.879498317239466</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7547505192417137</v>
+        <v>0.7797950873174631</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.3413924840417197</v>
+        <v>-0.278781063852346</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.527115348101965</v>
+        <v>2.564682200215589</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.882219055786246</v>
+        <v>-4.819607635596872</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8489970242209262</v>
+        <v>0.8740415922966756</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.2815018023991263</v>
+        <v>-0.2188903822097525</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.633339989409696</v>
+        <v>2.670906841523321</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.97995960041122</v>
+        <v>-4.917348180221847</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8245285424869802</v>
+        <v>0.8495731105627295</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.2973910805321064</v>
+        <v>-0.2347796603427327</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.638434158645952</v>
+        <v>2.676001010759576</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.15629736053415</v>
+        <v>-5.093685940344776</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7525294192624798</v>
+        <v>0.7775739873382292</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.4737288406550358</v>
+        <v>-0.4111174204656621</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.531167483396866</v>
+        <v>2.56873433551049</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.155607988372926</v>
+        <v>-5.092996568183553</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7512967861668978</v>
+        <v>0.7763413542426472</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.4737288406550358</v>
+        <v>-0.4111174204656621</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.529659101436795</v>
+        <v>2.567225953550419</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.162178953427519</v>
+        <v>-5.099567533238146</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7485312675804972</v>
+        <v>0.7735758356562465</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.4802998057096288</v>
+        <v>-0.417688385520255</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.525579389839475</v>
+        <v>2.563146241953099</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.154224983132747</v>
+        <v>-5.091613562943373</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7517128556984058</v>
+        <v>0.7767574237741552</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.4802998057096288</v>
+        <v>-0.417688385520255</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.525579389839475</v>
+        <v>2.563146241953099</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.14385160679966</v>
+        <v>-5.081240186610287</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7622439632594453</v>
+        <v>0.7872885313351947</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.4699264293765415</v>
+        <v>-0.4073150091871677</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.538185172667132</v>
+        <v>2.575752024780756</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.016167297005364</v>
+        <v>-4.95355587681599</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8182100605518885</v>
+        <v>0.8432546286276379</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.342242119582245</v>
+        <v>-0.2796306993928713</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.619688131918434</v>
+        <v>2.657254984032059</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.076833887407753</v>
+        <v>-5.01422246721838</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7806980968668049</v>
+        <v>0.8057426649425543</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.4239404363007787</v>
+        <v>-0.3613290161114049</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.557423814363187</v>
+        <v>2.594990666476811</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.011840027474108</v>
+        <v>-4.949228607284734</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8107933434508916</v>
+        <v>0.8358379115266412</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.3971098216966233</v>
+        <v>-0.3344984015072496</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.577619885736309</v>
+        <v>2.615186737849933</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.112598663231106</v>
+        <v>-5.049987243041732</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7746508287791705</v>
+        <v>0.7996953968549199</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.4859353904236288</v>
+        <v>-0.423323970234255</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.528485484131183</v>
+        <v>2.566052336244808</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.068395826145205</v>
+        <v>-5.005784405955832</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7982115661413678</v>
+        <v>0.8232561342171172</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.4417325533377283</v>
+        <v>-0.3791211331483545</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.56088678891056</v>
+        <v>2.598453641024185</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.105374853808648</v>
+        <v>-5.042763433619275</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7818299555452382</v>
+        <v>0.8068745236209875</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.4047586515463978</v>
+        <v>-0.342147231357024</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.581481130454606</v>
+        <v>2.619047982568231</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.125432932673489</v>
+        <v>-5.062821512484115</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.8250544891823419</v>
+        <v>0.8500990572580913</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.4047586515463978</v>
+        <v>-0.342147231357024</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.632728895637646</v>
+        <v>2.670295747751271</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.085502259495598</v>
+        <v>-5.022890839306225</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.8394674630477512</v>
+        <v>0.8645120311235006</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.3648279783685074</v>
+        <v>-0.3022165581791337</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.655128004138633</v>
+        <v>2.692694856252258</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.045031911932893</v>
+        <v>-4.98242049174352</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.850603830311103</v>
+        <v>0.8756483983868524</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.3243576308058025</v>
+        <v>-0.2617462106164287</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.674358440914526</v>
+        <v>2.711925293028151</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.979807730805688</v>
+        <v>-4.917196310616315</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.89388090685469</v>
+        <v>0.9189254749304394</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.2591334496785969</v>
+        <v>-0.1965220294892231</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.730680353683555</v>
+        <v>2.768247205797179</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.030302021162744</v>
+        <v>-4.967690600973371</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.8696441630111478</v>
+        <v>0.8946887310868974</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.3041541868046711</v>
+        <v>-0.2415427666152973</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.699628883707191</v>
+        <v>2.737195735820815</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-5.050413677197453</v>
+        <v>-4.987802257008079</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.8628562929285049</v>
+        <v>0.8879008610042542</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.2931268418072519</v>
+        <v>-0.2305154216178781</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.707502083036883</v>
+        <v>2.745068935150507</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.148094256470099</v>
+        <v>-5.085482836280725</v>
       </c>
       <c r="E1991" t="n">
-        <v>0.984341832240657</v>
+        <v>1.009386400316406</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.4038300371474407</v>
+        <v>-0.3412186169580669</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.80163793685398</v>
+        <v>2.839204788967604</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.590026363946009</v>
+        <v>3.82994646794227</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-5.121676325323208</v>
+        <v>-5.119461950306054</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.115021913917231</v>
+        <v>1.115907663924093</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.3774121060005504</v>
+        <v>-0.375197730983395</v>
       </c>
       <c r="G1992" t="n">
-        <v>2.937601604759931</v>
+        <v>2.938930229770225</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240612.xlsx
+++ b/tame_output/ON/bt/strategyON_20240612.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.9%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.7%</t>
+          <t>-50.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.3%</t>
+          <t>453.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-673.5%</t>
+          <t>-667.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-22.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-264.6%</t>
+          <t>-262.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.9%</t>
+          <t>-28.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.3%</t>
+          <t>-34.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-261.5%</t>
+          <t>-255.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-152.1%</t>
+          <t>-148.7%</t>
         </is>
       </c>
     </row>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83602339102496</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863223</v>
+        <v>3.821591150863224</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
@@ -47367,16 +47367,16 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-5.119461950306054</v>
+        <v>-5.061691267674583</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.115907663924093</v>
+        <v>1.139015936976681</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.375197730983395</v>
+        <v>-0.3174270483519246</v>
       </c>
       <c r="G1992" t="n">
-        <v>2.938930229770225</v>
+        <v>2.973592639349107</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240612.xlsx
+++ b/tame_output/ON/bt/strategyON_20240612.xlsx
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024961</v>
+        <v>3.83602339102496</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863224</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>

--- a/tame_output/ON/bt/strategyON_20240612.xlsx
+++ b/tame_output/ON/bt/strategyON_20240612.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-148.7%</t>
+          <t>-126.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1992"/>
+  <dimension ref="A1:G1993"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.82994646794227</v>
+        <v>3.81325185471488</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
@@ -47377,6 +47377,29 @@
       </c>
       <c r="G1992" t="n">
         <v>2.973592639349107</v>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" s="2" t="n">
+        <v>45455</v>
+      </c>
+      <c r="B1993" t="n">
+        <v>3.830208251386384</v>
+      </c>
+      <c r="C1993" t="n">
+        <v>3.202388455091612</v>
+      </c>
+      <c r="D1993" t="n">
+        <v>-5.061691267674583</v>
+      </c>
+      <c r="E1993" t="n">
+        <v>1.139015936976681</v>
+      </c>
+      <c r="F1993" t="n">
+        <v>-0.3174270483519246</v>
+      </c>
+      <c r="G1993" t="n">
+        <v>3.19545225207798</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240612.xlsx
+++ b/tame_output/ON/bt/strategyON_20240612.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-10.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.5%</t>
+          <t>-50.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.4%</t>
+          <t>453.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.9%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-667.7%</t>
+          <t>-660.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-50.3%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-262.3%</t>
+          <t>-259.5%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-126.5%</t>
+          <t>-125.5%</t>
         </is>
       </c>
     </row>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.092996568183553</v>
+        <v>-5.023237750838715</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7763413542426472</v>
+        <v>0.8042448811805825</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.4111174204656621</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83602339102496</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.099567533238146</v>
+        <v>-5.029808715893307</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7735758356562465</v>
+        <v>0.8014793625941818</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.417688385520255</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863223</v>
+        <v>3.821591150863224</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.091613562943373</v>
+        <v>-5.021854745598535</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7767574237741552</v>
+        <v>0.8046609507120905</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.417688385520255</v>
@@ -47045,10 +47045,10 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.081240186610287</v>
+        <v>-5.011481369265448</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7872885313351947</v>
+        <v>0.81519205827313</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.4073150091871677</v>
@@ -47068,10 +47068,10 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.95355587681599</v>
+        <v>-4.883797059471152</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8432546286276379</v>
+        <v>0.8711581555655732</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.2796306993928713</v>
@@ -47091,10 +47091,10 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.01422246721838</v>
+        <v>-4.944463649873541</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8057426649425543</v>
+        <v>0.8336461918804901</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.3613290161114049</v>
@@ -47114,10 +47114,10 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.949228607284734</v>
+        <v>-4.879469789939895</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8358379115266412</v>
+        <v>0.8637414384645767</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.3344984015072496</v>
@@ -47137,10 +47137,10 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.049987243041732</v>
+        <v>-4.980228425696893</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7996953968549199</v>
+        <v>0.8275989237928556</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.423323970234255</v>
@@ -47160,10 +47160,10 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.005784405955832</v>
+        <v>-4.936025588610993</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8232561342171172</v>
+        <v>0.8511596611550529</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.3791211331483545</v>
@@ -47183,10 +47183,10 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.042763433619275</v>
+        <v>-4.973004616274435</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8068745236209875</v>
+        <v>0.8347780505589233</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.342147231357024</v>
@@ -47206,10 +47206,10 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.062821512484115</v>
+        <v>-4.993062695139276</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.8500990572580913</v>
+        <v>0.8780025841960268</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.342147231357024</v>
@@ -47229,10 +47229,10 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.022890839306225</v>
+        <v>-4.953132021961386</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.8645120311235006</v>
+        <v>0.8924155580614361</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.3022165581791337</v>
@@ -47252,10 +47252,10 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.98242049174352</v>
+        <v>-4.912661674398681</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.8756483983868524</v>
+        <v>0.9035519253247881</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.2617462106164287</v>
@@ -47275,10 +47275,10 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.917196310616315</v>
+        <v>-4.847437493271475</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.9189254749304394</v>
+        <v>0.9468290018683752</v>
       </c>
       <c r="F1988" t="n">
         <v>-0.1965220294892231</v>
@@ -47298,10 +47298,10 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.967690600973371</v>
+        <v>-4.897931783628532</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.8946887310868974</v>
+        <v>0.9225922580248329</v>
       </c>
       <c r="F1989" t="n">
         <v>-0.2415427666152973</v>
@@ -47321,10 +47321,10 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.987802257008079</v>
+        <v>-4.91804343966324</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.8879008610042542</v>
+        <v>0.91580438794219</v>
       </c>
       <c r="F1990" t="n">
         <v>-0.2305154216178781</v>
@@ -47344,10 +47344,10 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.085482836280725</v>
+        <v>-5.015724018935886</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.009386400316406</v>
+        <v>1.037289927254342</v>
       </c>
       <c r="F1991" t="n">
         <v>-0.3412186169580669</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.81325185471488</v>
+        <v>3.813251854714881</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-5.061691267674583</v>
+        <v>-4.991932450329744</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.139015936976681</v>
+        <v>1.166919463914617</v>
       </c>
       <c r="F1992" t="n">
         <v>-0.3174270483519246</v>
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.830208251386384</v>
+        <v>3.841194794180673</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.202388455091612</v>
+        <v>3.211753664704896</v>
       </c>
       <c r="D1993" t="n">
-        <v>-5.061691267674583</v>
+        <v>-4.991932450329744</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.139015936976681</v>
+        <v>1.166919463914617</v>
       </c>
       <c r="F1993" t="n">
         <v>-0.3174270483519246</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.19545225207798</v>
+        <v>3.204817461691264</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240612.xlsx
+++ b/tame_output/ON/bt/strategyON_20240612.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.6%</t>
+          <t>126.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.2%</t>
+          <t>-50.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.6%</t>
+          <t>453.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-10.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-660.8%</t>
+          <t>-666.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.6%</t>
+          <t>-41.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-22.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-259.5%</t>
+          <t>-262.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.2%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-23.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-159.8%</t>
+          <t>-160.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-255.7%</t>
+          <t>-262.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.3%</t>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.896875313930094</v>
+        <v>-9.959486734119466</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8242996547491805</v>
+        <v>-0.8493442228249291</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.107908816136688</v>
+        <v>-2.170520236326061</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.870061605454592</v>
+        <v>1.832494753340968</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.10113348925996</v>
+        <v>-10.16374490944933</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9004897277624835</v>
+        <v>-0.925534295838232</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.235547760750677</v>
+        <v>-2.29815918094005</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.798991435804841</v>
+        <v>1.761424583691217</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.24294326346675</v>
+        <v>-10.30555468365612</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9527310829607623</v>
+        <v>-0.9777756510365117</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.406826558396252</v>
+        <v>-2.469437978585626</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.700706711701932</v>
+        <v>1.663139859588308</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.1694734317993</v>
+        <v>-10.23208485198867</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9079714488003621</v>
+        <v>-0.9330160168761106</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.333356726728804</v>
+        <v>-2.395968146918177</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.760160312195822</v>
+        <v>1.722593460082198</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.34459784918584</v>
+        <v>-10.40720926937521</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9634659950074624</v>
+        <v>-0.9885105630832109</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.508481144115347</v>
+        <v>-2.571092564304721</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.669640882511413</v>
+        <v>1.632074030397789</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.57904994320033</v>
+        <v>-10.6416613633897</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.064465997514854</v>
+        <v>-1.089510565590603</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.508481144115347</v>
+        <v>-2.571092564304721</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.662421717609817</v>
+        <v>1.624854865496193</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.86685378773757</v>
+        <v>-10.92946520792694</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.186259726103726</v>
+        <v>-1.211304294179474</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.796284988652586</v>
+        <v>-2.858896408841959</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.483067220113498</v>
+        <v>1.445500367999874</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.9196399433379</v>
+        <v>-10.98225136352727</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.2062583985053</v>
+        <v>-1.231302966581049</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.891960475234983</v>
+        <v>-2.954571895424356</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.426777718002616</v>
+        <v>1.389210865888992</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.04567673670618</v>
+        <v>-11.10828815689556</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.253979387223501</v>
+        <v>-1.27902395529925</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.86670885242524</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.444622420317576</v>
+        <v>1.407055568203952</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.99366122273737</v>
+        <v>-11.05627264292674</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.229182845949575</v>
+        <v>-1.254227414025324</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.86670885242524</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.448612756003977</v>
+        <v>1.411045903890353</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.13533306446149</v>
+        <v>-11.19794448465086</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.287326809537965</v>
+        <v>-1.312371377613713</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.86670885242524</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.447137529105235</v>
+        <v>1.409570676991611</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.08574222003666</v>
+        <v>-11.14835364022603</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.252437061603159</v>
+        <v>-1.277481629678908</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.817118008000406</v>
+        <v>-2.87972942818978</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.491945445925008</v>
+        <v>1.454378593811384</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.07293482703188</v>
+        <v>-11.13554624722125</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.260365238047932</v>
+        <v>-1.285409806123681</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.865973783009307</v>
+        <v>-2.928585203198681</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.449580847272984</v>
+        <v>1.41201399515936</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.84708967431247</v>
+        <v>-10.90970109450184</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.160448103923959</v>
+        <v>-1.185492671999709</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.824047107422143</v>
+        <v>-2.886658527611517</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.484315925661491</v>
+        <v>1.446749073547867</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.72251101797488</v>
+        <v>-10.78512243816425</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.109477496832863</v>
+        <v>-1.134522064908613</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.824047107422143</v>
+        <v>-2.886658527611517</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.48545507021755</v>
+        <v>1.447888218103926</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.77540630601917</v>
+        <v>-10.83801772620854</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.12800183788847</v>
+        <v>-1.153046405964219</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.819091761333697</v>
+        <v>-2.881703181523071</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.491062052032725</v>
+        <v>1.453495199919101</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.70327313073128</v>
+        <v>-10.76588455092066</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.093414863534681</v>
+        <v>-1.118459431610431</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.819091761333697</v>
+        <v>-2.881703181523071</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.496795756271362</v>
+        <v>1.459228904157738</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.63190673812164</v>
+        <v>-10.69451815831101</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.074605568884688</v>
+        <v>-1.099650136960437</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.747725368724049</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.529878329443286</v>
+        <v>1.492311477329662</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.36806987091757</v>
+        <v>-10.43068129110694</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9789543033159673</v>
+        <v>-1.003998871391717</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.747725368724049</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.519994848130378</v>
+        <v>1.482427996016754</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.10082807004917</v>
+        <v>-10.16343949023854</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8738921434679816</v>
+        <v>-0.898936711543731</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.747725368724049</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.518160287631004</v>
+        <v>1.48059343551738</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.00292103137268</v>
+        <v>-10.06553245156205</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8350296429708464</v>
+        <v>-0.8600742110465958</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.679739618863493</v>
+        <v>-2.742351039052866</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.558651422573877</v>
+        <v>1.521084570460253</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.978967490396721</v>
+        <v>-10.04157891058609</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8247797204349698</v>
+        <v>-0.8498242885107188</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.655786077887535</v>
+        <v>-2.718397498076909</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.573692053304945</v>
+        <v>1.536125201191321</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.714907552073925</v>
+        <v>-9.777518972263298</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7324160612676032</v>
+        <v>-0.7574606293433526</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.391726139564739</v>
+        <v>-2.454337559754113</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.718867700136871</v>
+        <v>1.681300848023247</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.007827928569087</v>
+        <v>-9.070439348758461</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4523712455259692</v>
+        <v>-0.4774158136017186</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.391726139564739</v>
+        <v>-2.454337559754113</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.71608066647657</v>
+        <v>1.678513814362946</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.967643630202897</v>
+        <v>-9.03025505039227</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4359539022916517</v>
+        <v>-0.460998470367401</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.351541841198548</v>
+        <v>-2.414153261387922</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.740534869384126</v>
+        <v>1.702968017270502</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.804243759263535</v>
+        <v>-8.866855179452909</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3712271326951502</v>
+        <v>-0.3962717007708996</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.188141970259186</v>
+        <v>-2.250753390448559</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.8379416131685</v>
+        <v>1.800374761054876</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.570762537033936</v>
+        <v>-8.633373957223309</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2699102149654578</v>
+        <v>-0.2949547830412071</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.954660748029587</v>
+        <v>-2.017272168218961</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.985954775344112</v>
+        <v>1.948387923230488</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.421096146026422</v>
+        <v>-8.483707566215795</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2129358688754115</v>
+        <v>-0.2379804369511609</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.861757256787051</v>
+        <v>-1.924368676976425</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.038804659776674</v>
+        <v>2.00123780766305</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.288820672395534</v>
+        <v>-8.351432092584908</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1646581926760295</v>
+        <v>-0.1897027607517789</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.729481783156165</v>
+        <v>-1.792093203345538</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.113537430702233</v>
+        <v>2.075970578588609</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.098220997722381</v>
+        <v>-8.160832417911754</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.08560326211913116</v>
+        <v>-0.1106478301948806</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.538882108483012</v>
+        <v>-1.601493528672385</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.230712296193762</v>
+        <v>2.193145444080137</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.8492211990388</v>
+        <v>-7.911832619228173</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.02690299857796008</v>
+        <v>0.001858430502210684</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.538882108483012</v>
+        <v>-1.601493528672385</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.24361863741742</v>
+        <v>2.206051785303796</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.954811188811904</v>
+        <v>-8.017422609001278</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1433089269305006</v>
+        <v>-0.16835349500625</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.644472098256116</v>
+        <v>-1.70708351844549</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.052288713954339</v>
+        <v>2.014721861840715</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.973546090930501</v>
+        <v>-8.036157511119875</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1022585459008529</v>
+        <v>-0.1273031139766023</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.650068107916247</v>
+        <v>-1.712679528105621</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.097475450035347</v>
+        <v>2.059908597921723</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.825606049522902</v>
+        <v>-7.888217469712275</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1629614520259808</v>
+        <v>-0.1880060201017302</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.62974719200769</v>
+        <v>-1.692358612197063</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.989789076892314</v>
+        <v>1.95222222477869</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.808447899391608</v>
+        <v>-7.871059319580981</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1648121782269412</v>
+        <v>-0.1898567463026906</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.612589041876396</v>
+        <v>-1.675200462065769</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.991369980717612</v>
+        <v>1.953803128603988</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.764899492620917</v>
+        <v>-7.827510912810291</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1543534276137581</v>
+        <v>-0.1793979956895075</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.612589041876396</v>
+        <v>-1.675200462065769</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.984409368622519</v>
+        <v>1.946842516508895</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.522751099167059</v>
+        <v>-7.585362519356432</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.04303171585107179</v>
+        <v>-0.06807628392682119</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.612589041876396</v>
+        <v>-1.675200462065769</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.998871723003662</v>
+        <v>1.961304870890038</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.414491962044537</v>
+        <v>-7.477103382233911</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.005195940542868094</v>
+        <v>-0.03024050861861749</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.612589041876396</v>
+        <v>-1.675200462065769</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.993403843462857</v>
+        <v>1.955836991349233</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.291200827227406</v>
+        <v>-7.35381224741678</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.04161860739456102</v>
+        <v>0.01657403931881163</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.489297907059265</v>
+        <v>-1.551909327248639</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.064876618363712</v>
+        <v>2.027309766250088</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.270051628323963</v>
+        <v>-7.332663048513337</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.05777926519326337</v>
+        <v>0.03273469711751398</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.468148708155822</v>
+        <v>-1.530760128345195</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.085267115943103</v>
+        <v>2.047700263829479</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.026286186340519</v>
+        <v>-7.088897606529892</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1510661503336919</v>
+        <v>0.1260215822579425</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.468148708155822</v>
+        <v>-1.530760128345195</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.081047824290154</v>
+        <v>2.04348097217653</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.924523366063224</v>
+        <v>-6.987134786252597</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1938955923646257</v>
+        <v>0.1688510242888763</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.454929639763393</v>
+        <v>-1.517541059952767</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.091103579245627</v>
+        <v>2.053536727132003</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.674672972114149</v>
+        <v>-6.737284392303523</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2865778249279578</v>
+        <v>0.2615332568522084</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.454929639763393</v>
+        <v>-1.517541059952767</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.08384565422933</v>
+        <v>2.046278802115705</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.498780879646716</v>
+        <v>-6.56139229983609</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3605337854355799</v>
+        <v>0.3354892173598305</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.454929639763393</v>
+        <v>-1.517541059952767</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.087444777749978</v>
+        <v>2.049877925636354</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.327334416624253</v>
+        <v>-6.389945836813626</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4424398766991189</v>
+        <v>0.4173953086233695</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.28348317674093</v>
+        <v>-1.346094596930303</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.20364016161801</v>
+        <v>2.166073309504386</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.10230141695543</v>
+        <v>-6.164912837144803</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.531473554182945</v>
+        <v>0.5064289861071956</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.058450177072107</v>
+        <v>-1.12106159726148</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.337680439035601</v>
+        <v>2.300113586921976</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.038665674721496</v>
+        <v>-6.101277094910869</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5616226521308358</v>
+        <v>0.5365780840550864</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9948144348381723</v>
+        <v>-1.057425855027546</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.380556685430278</v>
+        <v>2.342989833316654</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.994903493415654</v>
+        <v>-6.057514913605027</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5603217834369683</v>
+        <v>0.5352772153612189</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9948144348381723</v>
+        <v>-1.057425855027546</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.361750944214074</v>
+        <v>2.32418409210045</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.754472996610794</v>
+        <v>-5.817084416800167</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.65823705878379</v>
+        <v>0.6331924907080406</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7543839380333121</v>
+        <v>-0.8169953582226857</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.507752318921868</v>
+        <v>2.470185466808243</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.682230428439599</v>
+        <v>-5.744841848628973</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6910633998870881</v>
+        <v>0.6660188318113387</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7543839380333121</v>
+        <v>-0.8169953582226857</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.511681632756688</v>
+        <v>2.474114780643064</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.629232106158211</v>
+        <v>-5.691843526347585</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7129413127169832</v>
+        <v>0.6878967446412338</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6990476790313732</v>
+        <v>-0.7616590992207468</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.545561972075191</v>
+        <v>2.507995119961567</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.520427220678484</v>
+        <v>-5.583038640867858</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7534613381288673</v>
+        <v>0.7284167700531179</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6990476790313732</v>
+        <v>-0.7616590992207468</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.542560043295185</v>
+        <v>2.504993191181561</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.300406422641474</v>
+        <v>-5.363017842830847</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8430486943542856</v>
+        <v>0.8180041262785362</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.557827833963393</v>
+        <v>-0.6204392541527666</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.628870987346587</v>
+        <v>2.591304135232963</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.167538733578196</v>
+        <v>-5.230150153767569</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9120899527814199</v>
+        <v>0.8870453847056705</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.557827833963393</v>
+        <v>-0.6204392541527666</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.64476517014841</v>
+        <v>2.607198318034786</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.047365650213697</v>
+        <v>-5.109977070403071</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9613050305675213</v>
+        <v>0.9362604624917719</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.437654750598894</v>
+        <v>-0.5002661707882676</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.718014864607412</v>
+        <v>2.680448012493788</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.90269350511396</v>
+        <v>-4.965304925303333</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.029261991168856</v>
+        <v>1.004217423093107</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2929826054991566</v>
+        <v>-0.3555940256885302</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.814906254228694</v>
+        <v>2.77733940211507</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.962568332471652</v>
+        <v>-5.025179752661026</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9913495516272053</v>
+        <v>0.9663049835514559</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3528574328568487</v>
+        <v>-0.4154688530462223</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.765018849215505</v>
+        <v>2.72745199710188</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.875768834692643</v>
+        <v>-4.938380254882016</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.048469844061375</v>
+        <v>1.023425275985625</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3528574328568487</v>
+        <v>-0.4154688530462223</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.787419342538071</v>
+        <v>2.749852490424446</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.878238541154449</v>
+        <v>-4.940849961343822</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.047554362850065</v>
+        <v>1.022509794774315</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3553271393186549</v>
+        <v>-0.4179385595080285</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.786009920034399</v>
+        <v>2.748443067920775</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.946608727478459</v>
+        <v>-5.009220147667833</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.031213210795163</v>
+        <v>1.006168642719413</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3460514402824399</v>
+        <v>-0.4086628604718135</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.80258226193083</v>
+        <v>2.765015409817206</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.055146908394593</v>
+        <v>-5.117758328583967</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9782346470606003</v>
+        <v>0.9531900789848509</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3460514402824399</v>
+        <v>-0.4086628604718135</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.793018970562721</v>
+        <v>2.755452118449097</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.086140067723298</v>
+        <v>-5.148751487912672</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7905469483695051</v>
+        <v>0.7655023802937557</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3460514402824399</v>
+        <v>-0.4086628604718135</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.617728535603108</v>
+        <v>2.580161683489484</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.91066580793083</v>
+        <v>-4.973277228120203</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8653038842782803</v>
+        <v>0.8402593162025309</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3460514402824399</v>
+        <v>-0.4086628604718135</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.622295767594896</v>
+        <v>2.584728915481271</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.021602060572079</v>
+        <v>-5.084213480761452</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7966714119829876</v>
+        <v>0.7716268439072382</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3460514402824399</v>
+        <v>-0.4086628604718135</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.598037796356103</v>
+        <v>2.560470944242478</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.029884134717137</v>
+        <v>-5.092495554906511</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7964899675448698</v>
+        <v>0.7714453994691204</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3543335144274983</v>
+        <v>-0.4169449346168719</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.596199937088973</v>
+        <v>2.558633084975349</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.871958535781844</v>
+        <v>-4.934569955971218</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8698325935511195</v>
+        <v>0.8447880254753701</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3543335144274983</v>
+        <v>-0.4169449346168719</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.606372323521106</v>
+        <v>2.568805471407482</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.785715072755466</v>
+        <v>-4.84832649294484</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8992762493355309</v>
+        <v>0.8742316812597815</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3543335144274983</v>
+        <v>-0.4169449346168719</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.601318594094966</v>
+        <v>2.563751741981342</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.831021892154446</v>
+        <v>-4.89363331234382</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8729292970204645</v>
+        <v>0.8478847289447151</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3951436774367291</v>
+        <v>-0.4577550976261027</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.568608271733953</v>
+        <v>2.531041419620329</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.860054996856747</v>
+        <v>-4.922666417046121</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8618679281726456</v>
+        <v>0.8368233600968962</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3951436774367291</v>
+        <v>-0.4577550976261027</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.569160144767054</v>
+        <v>2.53159329265343</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.767244515405888</v>
+        <v>-4.829855935595261</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8282648126443553</v>
+        <v>0.8032202445686059</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3023331959858698</v>
+        <v>-0.3649446161752434</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.554119125528936</v>
+        <v>2.516552273415312</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.811633984735315</v>
+        <v>-4.874245404924689</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.812382500837185</v>
+        <v>0.7873379327614356</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3467226653152974</v>
+        <v>-0.409334085504671</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.52935891985588</v>
+        <v>2.491792067742256</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.698962766499065</v>
+        <v>-4.761574186688438</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.852526696643408</v>
+        <v>0.8274821285676586</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2340514470790472</v>
+        <v>-0.2966628672684208</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.592037359309353</v>
+        <v>2.554470507195729</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.586585765316392</v>
+        <v>-4.649197185505765</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9029687929471444</v>
+        <v>0.877924224871395</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2340514470790472</v>
+        <v>-0.2966628672684208</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.597528655140021</v>
+        <v>2.559961803026396</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.784820334203123</v>
+        <v>-4.847431754392496</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8351721671609913</v>
+        <v>0.8101275990852419</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.4322860159657778</v>
+        <v>-0.4948974361551514</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.490085115576521</v>
+        <v>2.452518263462897</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.867821615228402</v>
+        <v>-4.930433035417775</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.640327374751533</v>
+        <v>0.6152828066757836</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.4508569004929516</v>
+        <v>-0.5134683206823252</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.31729830486087</v>
+        <v>2.279731452747246</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.976435693671733</v>
+        <v>-5.039047113861106</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.717031404093406</v>
+        <v>0.6919868360176569</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.4508569004929516</v>
+        <v>-0.5134683206823252</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.437447965580076</v>
+        <v>2.399881113466451</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.063034276652836</v>
+        <v>-5.125645696842209</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6969049970032879</v>
+        <v>0.6718604289275385</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.4508569004929516</v>
+        <v>-0.5134683206823252</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.451960991682399</v>
+        <v>2.414394139568774</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.024650614094685</v>
+        <v>-5.087262034284058</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7096779033689171</v>
+        <v>0.6846333352931677</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4124732379348004</v>
+        <v>-0.475084658124174</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.472410630559658</v>
+        <v>2.434843778446034</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.847534284059519</v>
+        <v>-4.910145704248892</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7772534642282853</v>
+        <v>0.7522088961525359</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4124732379348004</v>
+        <v>-0.475084658124174</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.46913965940496</v>
+        <v>2.431572807291336</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.892626528893064</v>
+        <v>-4.955237949082438</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7598999580567802</v>
+        <v>0.7348553899810308</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.4743692811041902</v>
+        <v>-0.5369807012935638</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.432685425265239</v>
+        <v>2.395118573151615</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.713251107654297</v>
+        <v>-4.77586252784367</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8254371018587017</v>
+        <v>0.8003925337829523</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.3175925229334715</v>
+        <v>-0.3802039431228451</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.520538455474085</v>
+        <v>2.482971603360461</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.758265321174903</v>
+        <v>-4.820876741364277</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7882388717820488</v>
+        <v>0.7631943037062994</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.3479414182480761</v>
+        <v>-0.4105528384374497</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.483136573616912</v>
+        <v>2.445569721503288</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.025269831447338</v>
+        <v>-5.087881251636712</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6871286300120203</v>
+        <v>0.6620840619362709</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.5423044562910246</v>
+        <v>-0.6049158764803984</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.372210313130088</v>
+        <v>2.334643461016464</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.126467612884511</v>
+        <v>-5.189079033073885</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6458534393336528</v>
+        <v>0.6208088712579034</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.6107132698363438</v>
+        <v>-0.6733246900257175</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.330368946899398</v>
+        <v>2.292802094785774</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.093992026713739</v>
+        <v>-5.156603446903112</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6564436353562786</v>
+        <v>0.6313990672805292</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.6107132698363438</v>
+        <v>-0.6733246900257175</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.327968908453715</v>
+        <v>2.290402056340091</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.074953899006442</v>
+        <v>-5.137565319195815</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6605836056474423</v>
+        <v>0.6355390375716929</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.6688968811675383</v>
+        <v>-0.731508301356912</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.289583460863243</v>
+        <v>2.252016608749619</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.10608053015706</v>
+        <v>-5.168691950346433</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8257148221258754</v>
+        <v>0.800670254050126</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.6688968811675383</v>
+        <v>-0.731508301356912</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.467165329801924</v>
+        <v>2.4295984776883</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.158400910757852</v>
+        <v>-5.221012330947225</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8056199988716921</v>
+        <v>0.7805754307959427</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.6339500211586662</v>
+        <v>-0.6965614413480399</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.488966774793381</v>
+        <v>2.451399922679756</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.17865820928681</v>
+        <v>-5.241269629476183</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8035256098570351</v>
+        <v>0.7784810417812857</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.6339500211586662</v>
+        <v>-0.6965614413480399</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.494975305190307</v>
+        <v>2.457408453076682</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.030915239051807</v>
+        <v>-5.093526659241181</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9417754457430578</v>
+        <v>0.9167308776673084</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.466142663923783</v>
+        <v>-0.5287540841131567</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.674812367323259</v>
+        <v>2.637245515209634</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.132929921583028</v>
+        <v>-5.195541341772402</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9037631942620505</v>
+        <v>0.8787186261863011</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.466142663923783</v>
+        <v>-0.5287540841131567</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.67760598885474</v>
+        <v>2.640039136741115</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.126777215530244</v>
+        <v>-5.189388635719618</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9068866250748226</v>
+        <v>0.8818420569990733</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4599899578709987</v>
+        <v>-0.5226013780603724</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.681959960878069</v>
+        <v>2.644393108764444</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.143586513680746</v>
+        <v>-5.206197933870119</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8992433825547321</v>
+        <v>0.8741988144789827</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.4767992560215004</v>
+        <v>-0.5394106762108741</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.670954858727878</v>
+        <v>2.633388006614254</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.081288514904624</v>
+        <v>-5.143899935093997</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9904981358620017</v>
+        <v>0.9654535677862524</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.4767992560215004</v>
+        <v>-0.5394106762108741</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.737290412524699</v>
+        <v>2.699723560411075</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.879498317239466</v>
+        <v>-4.942109737428839</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7797950873174631</v>
+        <v>0.7547505192417137</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.278781063852346</v>
+        <v>-0.3413924840417197</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.564682200215589</v>
+        <v>2.527115348101965</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.819607635596872</v>
+        <v>-4.882219055786246</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8740415922966756</v>
+        <v>0.8489970242209262</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.2188903822097525</v>
+        <v>-0.2815018023991263</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.670906841523321</v>
+        <v>2.633339989409696</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.917348180221847</v>
+        <v>-4.97995960041122</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8495731105627295</v>
+        <v>0.8245285424869802</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.2347796603427327</v>
+        <v>-0.2973910805321064</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.676001010759576</v>
+        <v>2.638434158645952</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.093685940344776</v>
+        <v>-5.15629736053415</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7775739873382292</v>
+        <v>0.7525294192624798</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.4111174204656621</v>
+        <v>-0.4737288406550358</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.56873433551049</v>
+        <v>2.531167483396866</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.023237750838715</v>
+        <v>-5.084751037757273</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8042448811805825</v>
+        <v>0.7796395664131595</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.4111174204656621</v>
+        <v>-0.4737288406550358</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.567225953550419</v>
+        <v>2.529659101436795</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024961</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.029808715893307</v>
+        <v>-5.091322002811865</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8014793625941818</v>
+        <v>0.7768740478267584</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.417688385520255</v>
+        <v>-0.4802998057096288</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.563146241953099</v>
+        <v>2.525579389839475</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863224</v>
+        <v>3.821591150863222</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.021854745598535</v>
+        <v>-5.083368032517093</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8046609507120905</v>
+        <v>0.7800556359446675</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.417688385520255</v>
+        <v>-0.4802998057096288</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.563146241953099</v>
+        <v>2.525579389839475</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947583</v>
+        <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.011481369265448</v>
+        <v>-5.072994656184006</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.81519205827313</v>
+        <v>0.7905867435057066</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.4073150091871677</v>
+        <v>-0.4699264293765415</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.575752024780756</v>
+        <v>2.538185172667132</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326875</v>
+        <v>3.822707244326874</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.883797059471152</v>
+        <v>-4.94531034638971</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8711581555655732</v>
+        <v>0.8465528407981502</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.2796306993928713</v>
+        <v>-0.342242119582245</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.657254984032059</v>
+        <v>2.619688131918434</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314551</v>
+        <v>3.828837911314549</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.944463649873541</v>
+        <v>-5.005976936792099</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8336461918804901</v>
+        <v>0.8090408771130668</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.3613290161114049</v>
+        <v>-0.4239404363007787</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.594990666476811</v>
+        <v>2.557423814363187</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690026</v>
+        <v>3.816866067690024</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.879469789939895</v>
+        <v>-4.940983076858453</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8637414384645767</v>
+        <v>0.8391361236971537</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.3344984015072496</v>
+        <v>-0.3971098216966233</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.615186737849933</v>
+        <v>2.577619885736309</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674309</v>
+        <v>3.817961388674307</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.980228425696893</v>
+        <v>-5.041741712615451</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8275989237928556</v>
+        <v>0.8029936090254326</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.423323970234255</v>
+        <v>-0.4859353904236288</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.566052336244808</v>
+        <v>2.528485484131183</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163218</v>
+        <v>3.826713779163216</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.936025588610993</v>
+        <v>-4.997538875529551</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8511596611550529</v>
+        <v>0.8265543463876297</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.3791211331483545</v>
+        <v>-0.4417325533377283</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.598453641024185</v>
+        <v>2.56088678891056</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022903</v>
+        <v>3.838228663022901</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.973004616274435</v>
+        <v>-5.034517903192993</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8347780505589233</v>
+        <v>0.8101727357915003</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.342147231357024</v>
+        <v>-0.4047586515463978</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.619047982568231</v>
+        <v>2.581481130454606</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042137</v>
+        <v>3.863924114042136</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.993062695139276</v>
+        <v>-5.054575982057834</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.8780025841960268</v>
+        <v>0.8533972694286036</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.342147231357024</v>
+        <v>-0.4047586515463978</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.670295747751271</v>
+        <v>2.632728895637646</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078278</v>
+        <v>3.865367715078277</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.953132021961386</v>
+        <v>-5.014645308879944</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.8924155580614361</v>
+        <v>0.8678102432940129</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.3022165581791337</v>
+        <v>-0.3648279783685074</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.692694856252258</v>
+        <v>2.655128004138633</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232395</v>
+        <v>3.864518876232393</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.912661674398681</v>
+        <v>-4.974174961317239</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.9035519253247881</v>
+        <v>0.8789466105573649</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.2617462106164287</v>
+        <v>-0.3243576308058025</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.711925293028151</v>
+        <v>2.674358440914526</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162109</v>
+        <v>3.842576394162108</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.847437493271475</v>
+        <v>-4.908950780190033</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.9468290018683752</v>
+        <v>0.9222236871009519</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.1965220294892231</v>
+        <v>-0.2591334496785969</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.768247205797179</v>
+        <v>2.730680353683555</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639815</v>
+        <v>3.840090220639813</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.897931783628532</v>
+        <v>-4.95944507054709</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.9225922580248329</v>
+        <v>0.8979869432574099</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.2415427666152973</v>
+        <v>-0.3041541868046711</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.737195735820815</v>
+        <v>2.699628883707191</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749918</v>
+        <v>3.845198842749916</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.91804343966324</v>
+        <v>-4.979556726581798</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.91580438794219</v>
+        <v>0.8911990731747668</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.2305154216178781</v>
+        <v>-0.2931268418072519</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.745068935150507</v>
+        <v>2.707502083036883</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393543</v>
+        <v>3.828690479393542</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.015724018935886</v>
+        <v>-5.077237305854444</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.037289927254342</v>
+        <v>1.012684612486919</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.3412186169580669</v>
+        <v>-0.4038300371474407</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.839204788967604</v>
+        <v>2.80163793685398</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714881</v>
+        <v>3.813251854714879</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.991932450329744</v>
+        <v>-5.053445737248301</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.166919463914617</v>
+        <v>1.142314149147194</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.3174270483519246</v>
+        <v>-0.3800384685412984</v>
       </c>
       <c r="G1992" t="n">
-        <v>2.973592639349107</v>
+        <v>2.936025787235482</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,19 +47384,19 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.841194794180673</v>
+        <v>3.84119479418067</v>
       </c>
       <c r="C1993" t="n">
         <v>3.211753664704896</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.991932450329744</v>
+        <v>-5.053445737248301</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.166919463914617</v>
+        <v>1.142314149147194</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.3174270483519246</v>
+        <v>-0.3800384685412984</v>
       </c>
       <c r="G1993" t="n">
         <v>3.204817461691264</v>

--- a/tame_output/ON/bt/strategyON_20240612.xlsx
+++ b/tame_output/ON/bt/strategyON_20240612.xlsx
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>3.9%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-79.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-10.9%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.4%</t>
+          <t>-50.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.5%</t>
+          <t>453.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-666.9%</t>
+          <t>-672.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-262.0%</t>
+          <t>-265.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-125.5%</t>
+          <t>-153.3%</t>
         </is>
       </c>
     </row>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024959</v>
+        <v>3.83602339102496</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863222</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947581</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326874</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314549</v>
+        <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690024</v>
+        <v>3.816866067690026</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674307</v>
+        <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163216</v>
+        <v>3.826713779163218</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022901</v>
+        <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042136</v>
+        <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078277</v>
+        <v>3.865367715078278</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232393</v>
+        <v>3.864518876232395</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162108</v>
+        <v>3.842576394162109</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639813</v>
+        <v>3.840090220639815</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749916</v>
+        <v>3.845198842749918</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393542</v>
+        <v>3.828690479393543</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714879</v>
+        <v>3.813251854714881</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.84119479418067</v>
+        <v>3.841194794180673</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.211753664704896</v>
+        <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-5.053445737248301</v>
+        <v>-5.112064046753818</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.142314149147194</v>
+        <v>1.110574801358846</v>
       </c>
       <c r="F1993" t="n">
         <v>-0.3800384685412984</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.204817461691264</v>
+        <v>2.927733763249341</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240612.xlsx
+++ b/tame_output/ON/bt/strategyON_20240612.xlsx
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83602339102496</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863223</v>
+        <v>3.821591150863222</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947583</v>
+        <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326875</v>
+        <v>3.822707244326874</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314551</v>
+        <v>3.828837911314549</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690026</v>
+        <v>3.816866067690024</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674309</v>
+        <v>3.817961388674307</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163218</v>
+        <v>3.826713779163216</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022903</v>
+        <v>3.838228663022901</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042137</v>
+        <v>3.863924114042136</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078278</v>
+        <v>3.865367715078277</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232395</v>
+        <v>3.864518876232393</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162109</v>
+        <v>3.842576394162108</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639815</v>
+        <v>3.840090220639813</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749918</v>
+        <v>3.845198842749916</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393543</v>
+        <v>3.828690479393542</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714881</v>
+        <v>3.813251854714879</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.841194794180673</v>
+        <v>3.84119479418067</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-5.112064046753818</v>
+        <v>-5.112065078118392</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.110574801358846</v>
+        <v>1.110574388813016</v>
       </c>
       <c r="F1993" t="n">
         <v>-0.3800384685412984</v>
